--- a/DC/串讲.xlsx
+++ b/DC/串讲.xlsx
@@ -11,6 +11,9 @@
     <sheet name="单组件分析-进件管理组件" sheetId="3" r:id="rId2"/>
     <sheet name="调整内容" sheetId="2" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'产品业务流程+组件分析'!$A$1:$H$56</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -29,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="181">
   <si>
     <t>金融机构</t>
   </si>
@@ -61,7 +64,7 @@
     <t>公积金贷款（线上）</t>
   </si>
   <si>
-    <t>1、客户注册</t>
+    <t>1、客户注册认证</t>
   </si>
   <si>
     <t>渠道前端</t>
@@ -73,15 +76,15 @@
 4. 如需人脸/短信等，多因子策略已生效</t>
   </si>
   <si>
-    <t>客户注册</t>
+    <t>用户注册组件（渠道端）</t>
   </si>
   <si>
     <t>用户注册组件 → 
 客户管理组件（临时客户）、系统管理/消息/人脸/安全</t>
   </si>
   <si>
-    <t>先注册认证再申请；
-个人客户</t>
+    <t>1、先注册认证再申请（个人客户）；
+2、客户管理组件（办贷端）提供【临时客户创建接口】；</t>
   </si>
   <si>
     <t>2、查询产品信息</t>
@@ -100,8 +103,8 @@
 产品管理组件、利率与费用组件、额度管理组件、合同管理组件、预授信组件</t>
   </si>
   <si>
-    <t>展示产品列表/详情、利率优惠券、额度/合同可用额，并通过预授信组件展示预计可贷款金额，通过产品管理组件展示产品最高可贷款金额；
-本阶段不做黑/白名单拦截，是否可发起申请由后续申请前规则决定</t>
+    <t>1、展示产品列表/详情、利率优惠券、额度/合同可用额，并通过预授信组件展示预计可贷款金额，通过产品管理组件展示产品最高可贷款金额；
+2、本阶段不做黑/白名单拦截，是否可发起申请由后续申请前规则决定；</t>
   </si>
   <si>
     <t>3、客户发起贷款申请</t>
@@ -110,7 +113,7 @@
     <t>1. 调用时须能唯一识别客户：要么已有登录态和客户标识，要么在申请过程中可通过用户注册组件 + 客户管理组件创建临时客户；
 2. 若客户类型为对公，则在发起贷款/用信申请前必须已完成对公客户注册与基础认证（由用户注册组件 + 客户管理组件完成）；
 3. 已选定贷款/用信产品及目标授信/额度项（如适用）；
-4. 产品管理中已配置贷款申请要素与规则；
+4. 营销方案（产品）管理组件中已配置贷款申请要素与规则；
 5. 如产品要求“先预授信/先授权”，需能通过预授信组件或授权准入组件验证对应前置条件，否则可按“直接贷款”模式进入进件</t>
   </si>
   <si>
@@ -118,6 +121,7 @@
   </si>
   <si>
     <t>贷款申请组件 → 
+营销方案管理组件（申请页初始化）→ 
 风控组件（申请前规则包：反欺诈、黑/白名单、产品参数准入，按产品配置）→ 
 客户管理组件（补录）→ 
 客户授权准入组件 → 
@@ -128,9 +132,12 @@
 进件管理组件</t>
   </si>
   <si>
-    <t>提交前按产品配置执行申请前规则包：未通过则在本阶段直接拦截（不创建进件、也不进入授权）；
+    <t>客户需要先完成注册认证；
+申请页初始化由营销方案管理组件提供；
+提交前按产品配置执行申请前规则包：未通过则在本阶段直接拦截（不创建进件、也不进入授权）；
 通过后才进入授权准入与后续进件；
-授权协议展示由合同管理提供</t>
+授权协议展示由合同管理提供；
+申请内授权</t>
   </si>
   <si>
     <t>4、进件接收</t>
@@ -147,14 +154,126 @@
   <si>
     <t>进件管理组件 → 
 授权配置管理组件（查询进件阶段规则包 ID） →
-客户管理组件（补录）→ 
+客户管理组件→ 
 风控组件（准入，规则包由授权配置提供）→
 [R1]签约组件（生成签约任务）
 [R3]进件管理组件（转线下，按配置办贷任务类型）</t>
   </si>
   <si>
-    <t>晚同步：SIGNED 前不写客户/评级/授信/用信；
-进件准入规则包从授权配置（产品+阶段）取</t>
+    <t>1、晚同步：进件环节至落地进件信息，不同步/评级/授信/用信信息；
+2、按业务环阶段“产品+贷款进件阶段”查询当前需要执行的规则包；
+3、R1 转线下生成签约任务</t>
+  </si>
+  <si>
+    <t>（可选）客户发起提额申请</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 调用时须能唯一识别客户：要么已有登录态和客户标识，要么在申请过程中可通过用户注册组件 + 客户管理组件创建临时客户；
+2. 若客户类型为对公，则在发起贷款/用信申请前必须已完成对公客户注册与基础认证（由用户注册组件 + 客户管理组件完成）；
+3. 已选定贷款/用信产品及目标授信/额度项（如适用）；
+4. 营销方案（产品）管理组件中已配置贷款申请要素与规则；
+5. 如产品要求“先预授信/先授权”，需能通过预授信组件或授权准入组件验证对应前置条件，否则可按“直接贷款”模式进入进件
+</t>
+  </si>
+  <si>
+    <t>提额组件（渠道端）</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">提额组件 → 
+营销方案管理组件（申请页初始化）→ 
+风控组件（申请前规则包：反欺诈、黑/白名单、产品参数准入，按产品配置）→ 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">客户管理组件（补录）→ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">客户授权准入组件 → 
+授权配置管理组件 → 
+合同管理组件（授权协议可展示内容）→ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+消息/人脸 →
+签约组件（授权）→ 
+进件管理组件</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">客户需要先完成注册认证；
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>客户需要有前置的贷款申请；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+申请页初始化由营销方案管理组件提供；
+提交前按产品配置执行申请前规则包：未通过则在本阶段直接拦截（不创建进件、也不进入授权）；
+通过后才进入授权准入与后续进件；
+授权协议展示由合同管理提供；
+申请内授权</t>
+    </r>
+  </si>
+  <si>
+    <t>（可选）提额进件接收</t>
+  </si>
+  <si>
+    <t>1. 传入的申请/进件数据完整（至少包含产品、进件类型、客户标识、基本业务字段）；
+2. 对应产品在同步策略表中已有配置；
+3. 进件状态机定义完整；
+4. 如产品在授权配置中要求「先授权」，则在进件创建或进入关键状态前须可基于授权配置管理组件 + 授权记录校验该前置条件
+5、需要有前置的授信申请或贷款申请</t>
   </si>
   <si>
     <t>5、客户在线签借款合同</t>
@@ -164,7 +283,7 @@
 2. 如产品要求签约前风控/授权，需可获取对应规则包 ID 或在签约流程中触发</t>
   </si>
   <si>
-    <t>签约组件</t>
+    <t>签约组件（渠道端）</t>
   </si>
   <si>
     <t>签约组件 → 
@@ -175,11 +294,10 @@
 进件管理组件（状态）</t>
   </si>
   <si>
-    <t>签约完成触发晚同步一次性写业务表；
-展示内容由合同管理提供</t>
-  </si>
-  <si>
-    <t>6、客户发起提款</t>
+    <t>1、晚同步：合同签订完成，同步/评级/授信/用信信息，更新进件状态</t>
+  </si>
+  <si>
+    <t>6、客户发起提款申请</t>
   </si>
   <si>
     <t>1. 客户已签署必要合同/放款申请书（视产品而定）；
@@ -200,14 +318,36 @@
 进件管理组件</t>
   </si>
   <si>
-    <t>提款前风控/验证按产品配置
-更新进件状态</t>
+    <r>
+      <t xml:space="preserve">1、一个借款合同项下支持多次提款
+2、提款前风控/验证按产品配置
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3、提款环节需要签订放款申请书</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+4、更新进件状态
+</t>
+    </r>
   </si>
   <si>
     <t>湖北农信-公积金贷款（线上转线下）</t>
-  </si>
-  <si>
-    <t>客户注册管理组件</t>
   </si>
   <si>
     <t>进件管理组件 → 
@@ -218,13 +358,15 @@
 [R3]进件管理组件（转线下，按配置办贷任务类型）</t>
   </si>
   <si>
-    <t>同线上；进件规则包从授权配置取；R3 转线下</t>
+    <t>1、晚同步：进件环节至落地进件信息，不同步/评级/授信/用信信息
+2、按业务环阶段“产品+贷款进件阶段”查询当前需要执行的规则包
+3、R3 转线下</t>
   </si>
   <si>
     <t>5、客户经理个人客户创建</t>
   </si>
   <si>
-    <t>客户管理组件（办贷端）</t>
+    <t>办贷端</t>
   </si>
   <si>
     <t>1. 至少具备基础身份/组织信息；
@@ -232,10 +374,13 @@
 3. 外部来源需提供 external_source + external_customer_id</t>
   </si>
   <si>
+    <t>客户管理组件（办贷端）</t>
+  </si>
+  <si>
     <t>客户管理组件</t>
   </si>
   <si>
-    <t>线下补录/建档</t>
+    <t>建档/尽调补录</t>
   </si>
   <si>
     <t>6、客户经理线下三合一</t>
@@ -283,10 +428,7 @@
     <t>8、客户在线签借款合同</t>
   </si>
   <si>
-    <t>签约 → 晚同步 → 进件状态</t>
-  </si>
-  <si>
-    <t>9、客户发起提款</t>
+    <t>9、客户发起提款申请</t>
   </si>
   <si>
     <t>湖南农信</t>
@@ -295,40 +437,37 @@
     <t>公积金贷款</t>
   </si>
   <si>
-    <t>1、预授信申请</t>
-  </si>
-  <si>
-    <t>办贷端</t>
-  </si>
-  <si>
-    <t>1. 已确定预授信产品及客户（或名单）；
-2. 若按客户维度预授信，客户需具备基本身份信息；
-3. 系统已配置对应预授信规则包与额度策略</t>
-  </si>
-  <si>
-    <t>预授信申请组件（办贷端）</t>
-  </si>
-  <si>
-    <t>预授信组件 → 
-风控组件（白名单/规则）← 征信与外部数据管理组件</t>
-  </si>
-  <si>
-    <t>客户经理维护白名单</t>
+    <t>1、白名单维护</t>
+  </si>
+  <si>
+    <t>1. 对应阶段的规则包 ID 列表已通过授权配置管理/产品配置等确定；
+2. 必要输入数据（客户/进件/授信/用信/押品/外部数据等）可获取或通过征信与外部数据管理组件拉取；
+3. 外部数据源与风控引擎自身处于可用状态</t>
+  </si>
+  <si>
+    <t>名单管理组件</t>
+  </si>
+  <si>
+    <t>名单管理组件 → 
+风控组件（申请前规则包：反欺诈、黑/白名单、产品参数准入）</t>
+  </si>
+  <si>
+    <t>1、客户经理维护企业白名单；
+2、企业名单下增加客户白名单，调用“申请前规则包”进行业务基础准入，通过后保存名单信息；</t>
   </si>
   <si>
     <t>2、分享营销产品</t>
   </si>
   <si>
-    <t>渠道/客户经理（办贷端PAD）</t>
-  </si>
-  <si>
-    <t>营销方案管理组件</t>
+    <t>渠道前端/客户经理（办贷端PAD）</t>
   </si>
   <si>
     <t>营销方案管理组件（二维码/链接）</t>
   </si>
   <si>
-    <t>扫码获客</t>
+    <t>1、提供营销方案（产品）相关信息查询接口；
+2、提供二维码生成服务；
+3、提供二维码访问链接；</t>
   </si>
   <si>
     <t>客户注册认证（可选）</t>
@@ -338,28 +477,35 @@
 客户管理组件、系统管理/消息/人脸/安全</t>
   </si>
   <si>
-    <t>允许未注册直接申请，申请中可自动注册</t>
+    <t>1、允许未注册直接申请，申请中可自动注册；</t>
   </si>
   <si>
     <t>3、客户查询产品信息</t>
   </si>
   <si>
-    <t>展示产品列表/详情、利率优惠券、额度/合同可用额，并调用预授信组件查询预授信额度（预计可贷款金额）与产品管理组件提供的产品最高可贷款金额；本阶段不做黑/白名单拦截</t>
+    <t>1、展示产品列表/详情；
+2、本阶段不做黑/白名单拦截，是否可发起申请由后续申请前规则决定；</t>
   </si>
   <si>
     <t>4、客户发起贷款申请</t>
   </si>
   <si>
-    <t>营销方案管理组件（申请页初始化）→ 
-贷款申请组件 → 
+    <t>贷款申请组件 → 
+营销方案管理组件（申请页初始化）→ 
 风控组件（申请前规则包：反欺诈、黑/白名单、产品参数准入）→ 
 客户授权准入组件 → 
 授权配置管理/合同管理组件（授权协议展示）/消息/人脸 → 
 签约组件（授权）→ 
-进件管理组件；可选：用户注册+客户管理组件（自动注册/认证）</t>
-  </si>
-  <si>
-    <t>申请页初始化由营销方案管理组件提供（与 v1.2 CSV 一致）；因本产品允许未注册直接申请，黑/白名单等业务准入规则在提交贷款申请前统一由风控组件执行申请前规则包；可临时客户进件；申请内授权</t>
+进件管理组件；
+可选：用户注册+客户管理组件（自动注册/认证）</t>
+  </si>
+  <si>
+    <t>可临时客户进件；
+申请页初始化由营销方案管理组件提供；
+因本产品允许未注册直接申请，黑/白名单等业务准入规则在提交贷款申请前统一由风控组件执行申请前规则包：未通过则在本阶段直接拦截（不创建进件、也不进入授权）；
+通过后才进入授权准入与后续进件；
+授权协议展示由合同管理提供；
+申请内授权</t>
   </si>
   <si>
     <t>5、系统进件接收</t>
@@ -377,10 +523,17 @@
 [&gt;20W]进件管理组件（转线下）</t>
   </si>
   <si>
-    <t>早同步：RECEIVED 即初始化客户/评级/授信/用信；进件准入规则包 ID 从授权配置（产品+阶段）取</t>
-  </si>
-  <si>
-    <t>5～7、线下三合一/审批</t>
+    <t>1、早同步：进件环节至落地进件信息，同步/评级/授信/用信信息；
+2、按业务环阶段“产品+贷款进件阶段”查询当前需要执行的规则包；
+3、模型审批审批不通过直接拒绝；
+4、模型审批通过20万以下直接生成合同客户线上签订；
+5、模型审批通过20万以下需要转线下人工尽调后生成合同；</t>
+  </si>
+  <si>
+    <t>5～7、线下三合一与审批</t>
+  </si>
+  <si>
+    <t>办贷端-授信管理组件</t>
   </si>
   <si>
     <t>客户管理组件（办贷端）
@@ -391,7 +544,9 @@
     <t>同 1.2 第 5～7 阶段（客户管理组件、授信管理组件、工作流/审批流、合同管理组件、签约组件）</t>
   </si>
   <si>
-    <t>1、20W以上转线下分支</t>
+    <t>1、尽调补录 
+2、20W以上转线下分支
+3、审批通过后生成合同与签约任务</t>
   </si>
   <si>
     <t>签约组件 → 
@@ -403,219 +558,473 @@
 2、早同步下为更新而非首次写入</t>
   </si>
   <si>
+    <t>1、一个借款合同项下支持多次提款
+2、提款前风控/验证按产品配置
+3、更新进件状态</t>
+  </si>
+  <si>
     <t>长沙银行</t>
   </si>
   <si>
     <t>税E贷</t>
   </si>
   <si>
-    <t>办贷/外部</t>
-  </si>
-  <si>
-    <t>预授信组件 → 风控组件 ← 征信与外部数据管理组件</t>
-  </si>
-  <si>
-    <t>白名单维护或推送</t>
-  </si>
-  <si>
-    <t>2、客户注册认证</t>
-  </si>
-  <si>
-    <t>用户注册组件 → 客户管理组件、系统管理/消息/人脸/安全</t>
-  </si>
-  <si>
     <r>
-      <t>对公客户办理业务需要先在渠道端先完成注册认证</t>
+      <t>1、对公客户办理业务需要先在渠道端先完成注册认证</t>
     </r>
     <r>
       <rPr>
-        <sz val="11.25"/>
+        <sz val="11.5"/>
+        <color rgb="FF34495E"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，未完成不得进入后续授权</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
         <color rgb="FF34495E"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>，未完成不得进入后续授权/授信/进件流程</t>
-    </r>
-  </si>
-  <si>
-    <t>营销方案管理组件 → 产品管理组件、利率与费用组件、额度管理组件、合同管理组件、预授信组件、名单管理组件 → 客户授权准入组件</t>
-  </si>
-  <si>
-    <r>
-      <t>在产品列表/详情、优惠券、额度/合同可用额查询的基础上，增加两类额度展示服务：1）调用</t>
+      <t>/</t>
     </r>
     <r>
       <rPr>
-        <sz val="11.25"/>
-        <color rgb="FF2C3E50"/>
-        <rFont val="Arial"/>
+        <sz val="11.5"/>
+        <color rgb="FF34495E"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>预授信组件</t>
+      <t>授信</t>
     </r>
     <r>
       <rPr>
-        <sz val="11.25"/>
+        <sz val="11.5"/>
         <color rgb="FF34495E"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>查询预授信额度（预计可贷款金额）；2）调用</t>
+      <t>/</t>
     </r>
     <r>
       <rPr>
-        <sz val="11.25"/>
-        <color rgb="FF2C3E50"/>
-        <rFont val="Arial"/>
+        <sz val="11.5"/>
+        <color rgb="FF34495E"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>产品管理组件</t>
+      <t>进件流程</t>
+    </r>
+  </si>
+  <si>
+    <t>2、客户查询产品信息</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">营销方案管理组件 → 
+产品管理组件、利率与费用组件、额度管理组件、合同管理组件、预授信组件、名单管理组件 → 
+</t>
     </r>
     <r>
       <rPr>
-        <sz val="11.25"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>客户授权准入组件</t>
+    </r>
+  </si>
+  <si>
+    <t>1、展示产品列表/详情、
+2、本阶段不做黑/白名单拦截，是否可发起申请由后续申请前规则决定</t>
+  </si>
+  <si>
+    <t>3、客户授权准入</t>
+  </si>
+  <si>
+    <t>1. 已选定产品、客户类型、业务阶段（AUTHORIZATION/LOAN_APPLY/CREDIT_APPLY 等）；
+2. 客户及/或关联人已登录/可识别；
+3. 授权配置管理中针对「产品+客户类型+阶段」已存在配置（授权文件+适用关联人+规则包 + 授权检查模式）；
+4. 同一产品+客户类型+业务阶段下，若已存在有效未到期授权，则无需重新授权；若为补授权场景，可查询到历史授权记录用于提示，并根据“授权检查模式”（强制/仅提示/仅记录）决定缺失授权时是直接拦截还是仅提示后允许继续；
+5. （按产品配置）若本产品/阶段已配置前置业务准入规则（如行内规则、黑/白名单、基础参数准入等），则在调用本组件前应由上游完成前置检查且结果通过，检查未通过时不应再发起授权流程</t>
+  </si>
+  <si>
+    <t>客户授权准入组件</t>
+  </si>
+  <si>
+    <t>客户授权准入组件 → 
+授权配置管理组件 → 
+合同管理组件（授权协议展示）/消息 → 
+签约组件（授权）→ 
+风控组件（授权准入规则）</t>
+  </si>
+  <si>
+    <r>
+      <t>1、独立授权阶段</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF34495E"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，先授权后授信申请</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF34495E"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2、强依赖关联人授权（法人、实控人、主股东、关联企业等）</t>
+    </r>
+  </si>
+  <si>
+    <t>4、客户发起授信申请</t>
+  </si>
+  <si>
+    <t>授信申请组件（渠道端）</t>
+  </si>
+  <si>
+    <t>1. 调用时须能唯一识别客户：要么已有已注册/已认证的客户标识（如 customerId），要么本次申请过程中采集到足够的身份信息，可由客户管理组件创建临时客户；
+2. 若客户类型为对公，则在发起授信申请前必须已完成对公客户注册与基础认证（由用户注册组件 + 客户管理组件完成）；
+3. 已选定授信产品，且产品管理中已配置授信申请要素与校验规则；
+4. 营销方案（产品）管理组件中已配置授信申请要素与规则；
+5. 如产品要求“先预授信/先授权”，需能通过预授信组件或授权准入组件验证对应前置条件，否则可按“直接授信”模式进入进件</t>
+  </si>
+  <si>
+    <t>授信申请组件 → 
+营销方案管理组件（申请页初始化）→ 
+进件管理组件（授信进件）</t>
+  </si>
+  <si>
+    <t>1、客户需要先完成注册认证；
+2、申请页初始化由营销方案管理组件提供；
+3、单独的前置授权，渠道进件不重复授权，如果授权到期由客户经理在办贷端补充授权
+4、授信进件后转线下审批</t>
+  </si>
+  <si>
+    <t>5、股东会决议</t>
+  </si>
+  <si>
+    <t>企业负责人/办贷</t>
+  </si>
+  <si>
+    <t>1. 已识别对公客户与企业负责人；
+2. 已配置股东会决议适用的产品与场景；
+3. 已具备股东名单和通信方式（手机号、邮箱等）</t>
+  </si>
+  <si>
+    <t>股东会决议组件（渠道端）</t>
+  </si>
+  <si>
+    <t>股东会决议组件 → 
+征信与外部数据管理组件（工商/司法）→ 
+合同管理组件→
+合同（协议）模版管理组件→
+签约组件 → 
+消息中心</t>
+  </si>
+  <si>
+    <t>1、对公股东会决议签署；先查股东成员再下发签署任务推送签约中心；
+2、签约管理组件展示协议模板由合同管理提供
+3、发送股东会决议通知</t>
+  </si>
+  <si>
+    <t>6、系统进件接收</t>
+  </si>
+  <si>
+    <t>进件管理组件 → 
+授权配置管理组件（查询进件阶段规则包 ID） → 
+客户管理组件（创建）→ 
+风控组件（准入，规则包由授权配置提供）→ 
+评级管理组件 → 
+风控组件（额度）→ 
+授信管理组件（初始化）→ 
+用信管理组件（初始化）→ 
+进件管理组件（分配）</t>
+  </si>
+  <si>
+    <t>1、早同步：进件环节至落地进件信息，同步/评级/授信/用信信息（评级+授信+用信：三和一模式同步）；
+2、按业务环阶段“产品+授信进件阶段”查询当前需要执行的规则包；
+3、模型审批审批不通过直接拒绝；
+4、模型审批通过同意转线下客户经理人工处理（全部转人工）；</t>
+  </si>
+  <si>
+    <t>7、客户经理补录客户信息</t>
+  </si>
+  <si>
+    <t>8～10、利率/额度调整与额度激活</t>
+  </si>
+  <si>
+    <t>额度管理组件（办贷端）
+利率与费用组件（办贷端）</t>
+  </si>
+  <si>
+    <t>授信管理/额度管理组件 → 
+工作流/审批流组件 → 
+利率与费用组件/额度管理组件</t>
+  </si>
+  <si>
+    <t>显式额度激活与用信分离</t>
+  </si>
+  <si>
+    <t>11～12、三合一与审批</t>
+  </si>
+  <si>
+    <t>1、审批通过后生成授信合同与签约任务</t>
+  </si>
+  <si>
+    <t>13、客户在线签授信合同</t>
+  </si>
+  <si>
+    <t>渠道/进件</t>
+  </si>
+  <si>
+    <t>签约组件 → 
+合同管理组件（可展示内容）/消息/人脸 → 
+用信管理/授信管理/评级管理/合同管理组件（更新）→ 
+进件管理组件</t>
+  </si>
+  <si>
+    <t>多轮签约：先授信合同；展示内容由合同管理提供</t>
+  </si>
+  <si>
+    <t>14、客户发起提款申请</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1、一个授信合同项下支持多次提款
+2、提款前风控/验证按产品配置
+3、更新进件状态
+</t>
+  </si>
+  <si>
+    <t>政采贷</t>
+  </si>
+  <si>
+    <t>1、名单信息接收</t>
+  </si>
+  <si>
+    <t>政采平台/办贷</t>
+  </si>
+  <si>
+    <t>1、政采平台推送白名单（申请前规则包）；</t>
+  </si>
+  <si>
+    <t>2、客户注册认证</t>
+  </si>
+  <si>
+    <r>
+      <t>2、对公客户办理业务需要先在渠道端先完成注册认证</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF34495E"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，未完成不得进入后续授权</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
         <color rgb="FF34495E"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>查询产品最高可贷款额度；同时增加</t>
+      <t>/</t>
     </r>
     <r>
       <rPr>
-        <sz val="11.25"/>
-        <color rgb="FF2C3E50"/>
-        <rFont val="Arial"/>
+        <sz val="11.5"/>
+        <color rgb="FF34495E"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>前置检查：判断产品是否有黑/白名单限制及申请客户是否在名单中</t>
+      <t>授信</t>
     </r>
     <r>
       <rPr>
-        <sz val="11.25"/>
+        <sz val="11.5"/>
         <color rgb="FF34495E"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>；检查通过后从产品详情页进入独立的“客户授权准入”阶段</t>
-    </r>
-  </si>
-  <si>
-    <t>4、客户授权准入</t>
-  </si>
-  <si>
-    <t>客户授权准入组件 → 授权配置管理组件 → 合同管理组件（授权协议展示）/消息 → 签约组件（授权）→ 风控组件（授权准入规则）</t>
-  </si>
-  <si>
-    <r>
-      <t>独立授权阶段</t>
+      <t>/</t>
     </r>
     <r>
       <rPr>
-        <sz val="11.25"/>
+        <sz val="11.5"/>
         <color rgb="FF34495E"/>
-        <rFont val="Arial"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>，先授权后授信申请</t>
+      <t>进件流程</t>
     </r>
   </si>
   <si>
-    <t>5、客户发起授信申请</t>
-  </si>
-  <si>
-    <t>授信申请组件 → 进件管理组件（授信进件）</t>
-  </si>
-  <si>
-    <t>授信与贷款进件分离</t>
-  </si>
-  <si>
-    <t>6、股东会决议</t>
-  </si>
-  <si>
-    <t>企业负责人/办贷</t>
-  </si>
-  <si>
-    <t>股东会决议组件 → 征信与外部数据管理组件（工商/司法）→ 签约组件 → 合同管理组件（含模板与归档）、消息中心</t>
-  </si>
-  <si>
-    <t>对公股东会决议签署；先查股东成员再下发签署任务；展示内容由合同管理提供</t>
-  </si>
-  <si>
-    <t>6、系统进件接收</t>
-  </si>
-  <si>
-    <t>进件管理组件 → 客户管理组件 → 风控组件 → 评级管理组件 → 风控组件（额度）→ 授信管理组件（初始化）→ 用信管理组件（初始化）→ 进件管理组件（分配）</t>
-  </si>
-  <si>
     <r>
-      <t>早同步</t>
+      <t xml:space="preserve">1、展示产品列表/详情、
+</t>
     </r>
     <r>
       <rPr>
-        <sz val="11.25"/>
-        <color rgb="FF34495E"/>
-        <rFont val="Arial"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
+        <scheme val="minor"/>
       </rPr>
-      <t>；授信进件</t>
+      <t>2、发起授权申请时，前置检查：判断产品是否有黑/白名单限制及申请客户是否在名单中；检查通过后从产品详情页进入独立的“客户授权准入”阶段</t>
     </r>
   </si>
   <si>
-    <t>7、客户经理补录客户信息</t>
-  </si>
-  <si>
-    <t>建档/尽调补录</t>
-  </si>
-  <si>
-    <t>8～10、利率/额度调整与额度激活</t>
-  </si>
-  <si>
-    <t>授信管理/额度管理组件 → 工作流/审批流组件 → 利率与费用组件/额度管理组件</t>
-  </si>
-  <si>
-    <t>显式额度激活与用信分离</t>
-  </si>
-  <si>
-    <t>11～12、三合一与审批</t>
-  </si>
-  <si>
-    <t>授信管理组件 → 评级管理/授信管理/用信管理/风控组件 → 工作流/审批流组件 → 合同管理组件 → 签约组件</t>
-  </si>
-  <si>
-    <t>生成授信合同与签约任务</t>
-  </si>
-  <si>
-    <t>13、客户在线签授信合同</t>
-  </si>
-  <si>
-    <t>渠道/进件</t>
-  </si>
-  <si>
-    <t>签约组件 → 合同管理组件（可展示内容）/消息/人脸 → 用信管理/授信管理/评级管理/合同管理组件（更新）→ 进件管理组件</t>
-  </si>
-  <si>
-    <t>多轮签约：先授信合同；展示内容由合同管理提供</t>
-  </si>
-  <si>
-    <t>14、客户发起提款</t>
-  </si>
-  <si>
-    <t>放款组件（渠道）→ 用信管理/额度管理/合同管理组件 → 安全/人脸/消息 → 签约组件（放款申请书）→ 放款组件（办贷）→ 核心 → 进件管理组件</t>
-  </si>
-  <si>
-    <t>提款即用信</t>
-  </si>
-  <si>
-    <t>15、受托支付审批 / 16、还款</t>
-  </si>
-  <si>
-    <t>同 1.1</t>
-  </si>
-  <si>
-    <t>工作流/审批流组件 → 放款组件；还款组件链</t>
-  </si>
-  <si>
-    <t>按配置</t>
+    <t>4、客户授权准入</t>
+  </si>
+  <si>
+    <t>客户授权准入组件 → 
+授权配置管理组件（含关联人类型）→ 
+合同管理组件（授权协议展示）/消息 → 
+签约组件（授权）→ 
+风控组件</t>
+  </si>
+  <si>
+    <t>1、独立授权阶段，先授权后授信申请
+2、强依赖关联人授权（法人、实控人、主股东、关联企业等）</t>
+  </si>
+  <si>
+    <t>5、客户发起授信申请</t>
+  </si>
+  <si>
+    <t>6、股东会决议</t>
+  </si>
+  <si>
+    <t>进件管理组件 → 
+授权配置管理组件（查询进件阶段规则包 ID） → 
+客户管理组件（创建）→ 
+风控组件（准入，规则包由授权配置提供）→ 
+评级管理组件 → 
+风控组件（额度）→ 
+授信管理组件（初始化）→ 
+进件管理组件（分配）</t>
+  </si>
+  <si>
+    <t>1、早同步：进件环节至落地进件信息，同步/评级/授信信息（评级+授信“二合一模式同步，不生成用信信息）；
+2、按业务环阶段“产品+授信进件阶段”查询当前需要执行的规则包；
+3、模型审批审批不通过直接拒绝；
+4、模型审批通过同意转线下客户经理人工处理（全部转人工）；</t>
+  </si>
+  <si>
+    <t>11～12、二合一与审批</t>
+  </si>
+  <si>
+    <t>评级+授信（二合一模式）生成授信合同与签约任务</t>
+  </si>
+  <si>
+    <t>签约组件 → 
+合同管理组件（可展示内容）/消息/人脸 → 
+授信管理/评级管理/合同管理组件（更新）→ 
+进件管理组件</t>
+  </si>
+  <si>
+    <t>13、客户发起贷款申请</t>
+  </si>
+  <si>
+    <t>1. 调用时须能唯一识别客户：要么已有登录态和客户标识，要么在申请过程中可通过用户注册组件 + 客户管理组件创建临时客户；
+2. 若客户类型为对公，则在发起贷款/用信申请前必须已完成对公客户注册与基础认证（由用户注册组件 + 客户管理组件完成）；
+3. 已选定贷款/用信产品及目标授信/额度项（如适用）；
+4. 产品管理中已配置贷款申请要素与规则；
+5. 如产品要求“先预授信/先授权”，需能通过预授信组件或授权准入组件验证对应前置条件，否则可按“直接贷款”模式进入进件</t>
+  </si>
+  <si>
+    <t>贷款申请组件 → 
+营销方案管理组件（申请页初始化）→ 
+进件管理组件（授信进件）</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1、客户需要先完成注册认证；
+2、申请页初始化由营销方案管理组件提供；
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3、查询可融资采购合同信息，选择合同（单独组件）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+4、单独的前置授权，渠道进件不重复授权，如果授权到期由客户经理在办贷端补充授权
+3、额度项下发起贷款申请进件后转线下审批</t>
+    </r>
+  </si>
+  <si>
+    <t>14、系统进件接收</t>
+  </si>
+  <si>
+    <t>进件管理组件 → 
+授权配置管理组件（查询进件阶段规则包 ID） → 
+风控组件（准入，规则包由授权配置提供）→ 
+用信管理组件（初始化）→ 
+进件管理组件（分配）→</t>
+  </si>
+  <si>
+    <t>1、早同步：进件环节至落地进件信息，同步用信信息（单独用信同步）；
+2、按业务环阶段“产品+贷款进件阶段”查询当前需要执行的规则包；
+3、模型审批审批不通过直接拒绝；
+4、模型审批通过同意转线下客户经理人工处理（全部转人工）；</t>
+  </si>
+  <si>
+    <t>15～16、单独用信申请与审批</t>
+  </si>
+  <si>
+    <t>办贷端-用信管理组件</t>
+  </si>
+  <si>
+    <t>用信管理组件（办贷端）
+工作流/审批流组件（办贷端）</t>
+  </si>
+  <si>
+    <t>用信申报审批阶段（用信管理组件、工作流/审批流、合同管理组件、签约组件）</t>
+  </si>
+  <si>
+    <t>单独用信申报审批，生成借款合同与签约任务</t>
+  </si>
+  <si>
+    <t>17、客户在线签借款合同</t>
+  </si>
+  <si>
+    <t>多轮签约：借款合同；展示内容由合同管理提供</t>
+  </si>
+  <si>
+    <t>18、客户发起提款申请</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1、一个借款合同项下支持多次提款
+2、提款前风控/验证按产品配置
+3、更新进件状态
+</t>
   </si>
   <si>
     <t>客户预约 -----&gt;进件任务</t>
@@ -661,7 +1070,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -822,19 +1231,41 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.25"/>
-      <color rgb="FF2C3E50"/>
+      <sz val="11.5"/>
+      <color rgb="FF34495E"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11.5"/>
+      <color rgb="FF34495E"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11.25"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.5"/>
       <color rgb="FF34495E"/>
-      <name val="Arial"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -849,7 +1280,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.05"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1187,7 +1630,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1211,16 +1654,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1229,89 +1672,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1323,41 +1766,74 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1885,1283 +2361,1682 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="15.125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="34.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="27.75" style="1" customWidth="1"/>
     <col min="4" max="4" width="34.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="70.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="28.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="74.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="28.75" style="1" customWidth="1"/>
     <col min="7" max="7" width="62.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="50.625" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" spans="1:8">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="54" spans="1:8">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="81" spans="1:8">
-      <c r="A3" s="6" t="s">
+    <row r="3" s="1" customFormat="1" ht="67.5" spans="1:8">
+      <c r="A3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="135" spans="1:8">
-      <c r="A4" s="6" t="s">
+    <row r="4" s="1" customFormat="1" ht="148.5" spans="1:8">
+      <c r="A4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" ht="81" spans="1:8">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="10" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" ht="81" spans="1:8">
-      <c r="A6" s="6" t="s">
+    <row r="6" ht="148.5" spans="1:8">
+      <c r="A6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="7" t="s">
+      <c r="D6" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" ht="94.5" spans="1:8">
-      <c r="A7" s="6" t="s">
+    <row r="7" ht="81" spans="1:8">
+      <c r="A7" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="7" t="s">
+      <c r="D7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" ht="54" spans="1:8">
+      <c r="F7" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" ht="81" spans="1:8">
       <c r="A8" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" ht="81" spans="1:8">
+    </row>
+    <row r="9" s="2" customFormat="1" ht="94.5" spans="1:8">
       <c r="A9" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>11</v>
       </c>
       <c r="E9" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" ht="54" spans="1:8">
+      <c r="A10" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" ht="67.5" spans="1:8">
+      <c r="A11" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F11" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G11" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H11" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" ht="135" spans="1:8">
-      <c r="A10" s="9" t="s">
+    <row r="12" s="2" customFormat="1" ht="148.5" spans="1:8">
+      <c r="A12" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B12" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" ht="81" spans="1:8">
+      <c r="A13" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" ht="148.5" spans="1:8">
+      <c r="A14" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="81" spans="1:8">
+      <c r="A15" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" s="3" customFormat="1" ht="87" customHeight="1" spans="1:8">
+      <c r="A16" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" s="3" customFormat="1" ht="81" spans="1:8">
+      <c r="A17" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" s="3" customFormat="1" ht="54" spans="1:8">
+      <c r="A18" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" ht="81" spans="1:8">
+      <c r="A19" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="G19" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="H19" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" ht="94.5" spans="1:8">
+      <c r="A20" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H20" s="20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" ht="54" spans="1:8">
+      <c r="A21" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" ht="67.5" spans="1:8">
+      <c r="A22" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="G22" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" ht="54" spans="1:8">
+      <c r="A23" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" ht="67.5" spans="1:8">
+      <c r="A24" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" ht="108" spans="1:8">
+      <c r="A25" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F25" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" ht="81" spans="1:8">
-      <c r="A11" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="12" t="s">
+      <c r="G25" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" ht="135" spans="1:8">
+      <c r="A26" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E26" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="12"/>
-      <c r="G11" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" s="3" customFormat="1" ht="87" customHeight="1" spans="1:8">
-      <c r="A12" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" s="3" customFormat="1" ht="81" spans="1:8">
-      <c r="A13" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="H13" s="15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" s="3" customFormat="1" ht="54" spans="1:8">
-      <c r="A14" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="H14" s="15" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" ht="81" spans="1:8">
-      <c r="A15" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" ht="94.5" spans="1:8">
-      <c r="A16" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" ht="40.5" spans="1:8">
-      <c r="A17" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E17" s="7" t="s">
+      <c r="F26" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" s="3" customFormat="1" ht="40.5" spans="1:8">
+      <c r="A27" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="E27" s="18"/>
+      <c r="F27" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="H27" s="19" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" ht="40.5" spans="1:8">
+      <c r="A28" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="10" t="s">
         <v>67</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="18" ht="81" spans="1:8">
-      <c r="A18" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19" ht="54" spans="1:8">
-      <c r="A19" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="20" ht="81" spans="1:8">
-      <c r="A20" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="21" ht="108" spans="1:8">
-      <c r="A21" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" ht="135" spans="1:8">
-      <c r="A22" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="23" s="3" customFormat="1" ht="40.5" spans="1:8">
-      <c r="A23" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E23" s="14"/>
-      <c r="F23" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="H23" s="15" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="24" ht="40.5" spans="1:8">
-      <c r="A24" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" ht="94.5" spans="1:8">
-      <c r="A25" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" spans="1:8">
-      <c r="A26" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="H26" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" ht="27.75" spans="1:8">
-      <c r="A27" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" ht="83.25" spans="1:8">
-      <c r="A28" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>79</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
+      <c r="E28" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>40</v>
+      </c>
       <c r="G28" s="10" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" ht="27" spans="1:8">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" ht="94.5" spans="1:8">
       <c r="A29" s="9" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>103</v>
+        <v>70</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
+      <c r="E29" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>45</v>
+      </c>
       <c r="G29" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" ht="54" spans="1:8">
+      <c r="A30" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H30" s="20" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" ht="67.5" spans="1:8">
+      <c r="A31" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="H31" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="H29" s="10" t="s">
+    </row>
+    <row r="32" s="2" customFormat="1" ht="148.5" spans="1:8">
+      <c r="A32" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32" s="14" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="1:8">
-      <c r="A30" s="9" t="s">
+      <c r="D32" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="H32" s="20" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" ht="117" customHeight="1" spans="1:8">
+      <c r="A33" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" ht="81" spans="1:8">
+      <c r="A34" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" ht="121.5" spans="1:8">
+      <c r="A35" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" ht="40.5" spans="1:8">
+      <c r="A36" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H36" s="14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" ht="40.5" spans="1:8">
+      <c r="A37" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C37" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="D37" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="F37" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="G37" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="H37" s="22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" s="3" customFormat="1" ht="40.5" spans="1:8">
+      <c r="A38" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="E38" s="18"/>
+      <c r="F38" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="G38" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="H38" s="19" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" ht="54" spans="1:8">
+      <c r="A39" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="H39" s="14" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="40" s="2" customFormat="1" ht="94.5" spans="1:8">
+      <c r="A40" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G40" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H40" s="14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="41" s="4" customFormat="1" ht="54" spans="1:8">
+      <c r="A41" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B41" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C41" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="E41" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="F41" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="G41" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="H41" s="21" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="42" s="4" customFormat="1" ht="54" spans="1:8">
+      <c r="A42" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B42" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C42" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="D42" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="H42" s="20" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="43" s="4" customFormat="1" ht="67.5" spans="1:8">
+      <c r="A43" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="C43" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="D43" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="F43" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="H43" s="26" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="44" s="4" customFormat="1" ht="148.5" spans="1:8">
+      <c r="A44" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B44" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C44" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="D44" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="F44" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="G44" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="H44" s="21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="45" s="4" customFormat="1" ht="108" spans="1:8">
+      <c r="A45" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="D45" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="E45" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="F45" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="G45" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="H45" s="21" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46" s="4" customFormat="1" ht="81" spans="1:8">
+      <c r="A46" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B46" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C46" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="D46" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="E46" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="F46" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="G46" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="H46" s="21" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47" s="4" customFormat="1" ht="108" spans="1:8">
+      <c r="A47" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B47" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C47" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="D47" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="E47" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F47" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="G47" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="H47" s="21" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="48" s="4" customFormat="1" ht="40.5" spans="1:8">
+      <c r="A48" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B48" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C48" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="D48" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="E48" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="F48" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G48" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="H48" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" s="4" customFormat="1" ht="40.5" spans="1:8">
+      <c r="A49" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B49" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C49" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="D49" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="E49" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="F49" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="G49" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="H49" s="22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="50" s="3" customFormat="1" ht="40.5" spans="1:8">
+      <c r="A50" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B50" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="C50" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="D50" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="E50" s="18"/>
+      <c r="F50" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="G50" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="H50" s="19" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="51" s="4" customFormat="1" ht="54" spans="1:8">
+      <c r="A51" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B51" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C51" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="E51" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="F51" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="G51" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="H51" s="21" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="52" s="4" customFormat="1" ht="108" spans="1:8">
+      <c r="A52" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B52" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="C52" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="D52" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="F52" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="G52" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="H52" s="26" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="53" s="4" customFormat="1" ht="94.5" spans="1:8">
+      <c r="A53" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="C53" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="D53" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F53" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="G53" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="H53" s="21" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="54" s="3" customFormat="1" ht="27" spans="1:8">
+      <c r="A54" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B54" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="D54" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="E54" s="18"/>
+      <c r="F54" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="G54" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="H54" s="19" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="55" s="4" customFormat="1" ht="54" spans="1:8">
+      <c r="A55" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B55" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C55" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="D55" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="H30" s="10" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" ht="27" spans="1:8">
-      <c r="A31" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" ht="40.5" spans="1:8">
-      <c r="A32" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="H32" s="10" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" spans="1:8">
-      <c r="A33" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" ht="27" spans="1:8">
-      <c r="A34" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="35" s="2" customFormat="1" ht="27" spans="1:8">
-      <c r="A35" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" ht="27" spans="1:8">
-      <c r="A36" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="37" s="2" customFormat="1" ht="40.5" spans="1:8">
-      <c r="A37" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="D37" s="9" t="s">
+      <c r="E55" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="F55" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="G55" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="H55" s="21" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="56" s="4" customFormat="1" ht="94.5" spans="1:8">
+      <c r="A56" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B56" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C56" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="D56" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="38" s="2" customFormat="1" ht="27" spans="1:8">
-      <c r="A38" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="H38" s="10" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="12"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="12"/>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="12"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="12"/>
-      <c r="B41" s="12"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
-      <c r="H41" s="12"/>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="12"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="12"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="12"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="12"/>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="12"/>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
-      <c r="H45" s="12"/>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="12"/>
-      <c r="B46" s="12"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="12"/>
-      <c r="B47" s="12"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="12"/>
-      <c r="H47" s="12"/>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="12"/>
-      <c r="B48" s="12"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12"/>
-      <c r="H48" s="12"/>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="12"/>
-      <c r="B49" s="12"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="12"/>
-      <c r="H49" s="12"/>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="12"/>
-      <c r="B50" s="12"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12"/>
-      <c r="G50" s="12"/>
-      <c r="H50" s="12"/>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="12"/>
-      <c r="B51" s="12"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="12"/>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="12"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="12"/>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="12"/>
-      <c r="B53" s="12"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="12"/>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="12"/>
-      <c r="B54" s="12"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="12"/>
-      <c r="B55" s="12"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56" s="12"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
+      <c r="E56" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F56" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="G56" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H56" s="21" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="12"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
+      <c r="A57" s="16"/>
+      <c r="B57" s="17"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="16"/>
+      <c r="H57" s="16"/>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="12"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
+      <c r="A58" s="16"/>
+      <c r="B58" s="17"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="16"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="16"/>
+      <c r="H58" s="16"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="12"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="12"/>
-      <c r="G59" s="12"/>
-      <c r="H59" s="12"/>
+      <c r="A59" s="16"/>
+      <c r="B59" s="17"/>
+      <c r="C59" s="16"/>
+      <c r="D59" s="16"/>
+      <c r="E59" s="16"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="16"/>
+      <c r="H59" s="16"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="12"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="12"/>
-      <c r="E60" s="12"/>
-      <c r="F60" s="12"/>
-      <c r="G60" s="12"/>
-      <c r="H60" s="12"/>
+      <c r="A60" s="16"/>
+      <c r="B60" s="17"/>
+      <c r="C60" s="16"/>
+      <c r="D60" s="16"/>
+      <c r="E60" s="16"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="16"/>
+      <c r="H60" s="16"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="12"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="12"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="12"/>
-      <c r="G61" s="12"/>
-      <c r="H61" s="12"/>
+      <c r="A61" s="16"/>
+      <c r="B61" s="17"/>
+      <c r="C61" s="16"/>
+      <c r="D61" s="16"/>
+      <c r="E61" s="16"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="16"/>
+      <c r="H61" s="16"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="12"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="12"/>
-      <c r="E62" s="12"/>
-      <c r="F62" s="12"/>
-      <c r="G62" s="12"/>
-      <c r="H62" s="12"/>
+      <c r="A62" s="16"/>
+      <c r="B62" s="17"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="16"/>
+      <c r="E62" s="16"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="16"/>
+      <c r="H62" s="16"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="12"/>
-      <c r="B63" s="12"/>
-      <c r="C63" s="12"/>
-      <c r="D63" s="12"/>
-      <c r="E63" s="12"/>
-      <c r="F63" s="12"/>
-      <c r="G63" s="12"/>
-      <c r="H63" s="12"/>
+      <c r="A63" s="16"/>
+      <c r="B63" s="17"/>
+      <c r="C63" s="16"/>
+      <c r="D63" s="16"/>
+      <c r="E63" s="16"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="16"/>
+      <c r="H63" s="16"/>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="12"/>
-      <c r="B64" s="12"/>
-      <c r="C64" s="12"/>
-      <c r="D64" s="12"/>
-      <c r="E64" s="12"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="12"/>
-      <c r="H64" s="12"/>
+      <c r="A64" s="16"/>
+      <c r="B64" s="17"/>
+      <c r="C64" s="16"/>
+      <c r="D64" s="16"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="16"/>
+      <c r="H64" s="16"/>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="12"/>
-      <c r="B65" s="12"/>
-      <c r="C65" s="12"/>
-      <c r="D65" s="12"/>
-      <c r="E65" s="12"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="12"/>
-      <c r="H65" s="12"/>
+      <c r="A65" s="16"/>
+      <c r="B65" s="17"/>
+      <c r="C65" s="16"/>
+      <c r="D65" s="16"/>
+      <c r="E65" s="16"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="16"/>
+      <c r="H65" s="16"/>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="12"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="12"/>
-      <c r="E66" s="12"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="12"/>
-      <c r="H66" s="12"/>
+      <c r="A66" s="16"/>
+      <c r="B66" s="17"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="16"/>
+      <c r="E66" s="16"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="16"/>
+      <c r="H66" s="16"/>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="12"/>
-      <c r="B67" s="12"/>
-      <c r="C67" s="12"/>
-      <c r="D67" s="12"/>
-      <c r="E67" s="12"/>
-      <c r="F67" s="12"/>
-      <c r="G67" s="12"/>
-      <c r="H67" s="12"/>
+      <c r="A67" s="16"/>
+      <c r="B67" s="17"/>
+      <c r="C67" s="16"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="16"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="16"/>
+      <c r="H67" s="16"/>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="12"/>
-      <c r="B68" s="12"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="12"/>
-      <c r="E68" s="12"/>
-      <c r="F68" s="12"/>
-      <c r="G68" s="12"/>
-      <c r="H68" s="12"/>
+      <c r="A68" s="16"/>
+      <c r="B68" s="17"/>
+      <c r="C68" s="16"/>
+      <c r="D68" s="16"/>
+      <c r="E68" s="16"/>
+      <c r="F68" s="16"/>
+      <c r="G68" s="16"/>
+      <c r="H68" s="16"/>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="12"/>
-      <c r="B69" s="12"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="12"/>
-      <c r="E69" s="12"/>
-      <c r="F69" s="12"/>
-      <c r="G69" s="12"/>
-      <c r="H69" s="12"/>
+      <c r="A69" s="16"/>
+      <c r="B69" s="17"/>
+      <c r="C69" s="16"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="16"/>
+      <c r="H69" s="16"/>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="12"/>
-      <c r="B70" s="12"/>
-      <c r="C70" s="12"/>
-      <c r="D70" s="12"/>
-      <c r="E70" s="12"/>
-      <c r="F70" s="12"/>
-      <c r="G70" s="12"/>
-      <c r="H70" s="12"/>
+      <c r="A70" s="16"/>
+      <c r="B70" s="17"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="16"/>
+      <c r="H70" s="16"/>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71" s="12"/>
-      <c r="B71" s="12"/>
-      <c r="C71" s="12"/>
-      <c r="D71" s="12"/>
-      <c r="E71" s="12"/>
-      <c r="F71" s="12"/>
-      <c r="G71" s="12"/>
-      <c r="H71" s="12"/>
+      <c r="A71" s="16"/>
+      <c r="B71" s="17"/>
+      <c r="C71" s="16"/>
+      <c r="D71" s="16"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="16"/>
+      <c r="H71" s="16"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="16"/>
+      <c r="B72" s="17"/>
+      <c r="C72" s="16"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="16"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="16"/>
+      <c r="H72" s="16"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="16"/>
+      <c r="B73" s="17"/>
+      <c r="C73" s="16"/>
+      <c r="D73" s="16"/>
+      <c r="E73" s="16"/>
+      <c r="F73" s="16"/>
+      <c r="G73" s="16"/>
+      <c r="H73" s="16"/>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="16"/>
+      <c r="B74" s="17"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="16"/>
+      <c r="H74" s="16"/>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="16"/>
+      <c r="B75" s="17"/>
+      <c r="C75" s="16"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="16"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="16"/>
+      <c r="H75" s="16"/>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="16"/>
+      <c r="B76" s="17"/>
+      <c r="C76" s="16"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="16"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="16"/>
+      <c r="H76" s="16"/>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="16"/>
+      <c r="B77" s="17"/>
+      <c r="C77" s="16"/>
+      <c r="D77" s="16"/>
+      <c r="E77" s="16"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="16"/>
+      <c r="H77" s="16"/>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H56" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -3189,57 +4064,57 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>138</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>139</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>140</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>141</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>142</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>143</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>144</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>145</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
